--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.14136160317389</v>
+        <v>9.610471260515757</v>
       </c>
       <c r="D2" t="n">
-        <v>56.82877377830724</v>
+        <v>9.234675738974927</v>
       </c>
       <c r="E2" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F2" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.85146696077596</v>
+        <v>3.875863381126093</v>
       </c>
       <c r="D3" t="n">
-        <v>21.12627565874803</v>
+        <v>3.433019794546555</v>
       </c>
       <c r="E3" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F3" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.97692669225939</v>
+        <v>5.846250587492151</v>
       </c>
       <c r="D4" t="n">
-        <v>30.70011818406853</v>
+        <v>4.988769204911136</v>
       </c>
       <c r="E4" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F4" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.30160780346966</v>
+        <v>8.98651126806382</v>
       </c>
       <c r="D5" t="n">
-        <v>52.36090071019063</v>
+        <v>8.508646365405978</v>
       </c>
       <c r="E5" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F5" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.18359575286797</v>
+        <v>10.10483430984105</v>
       </c>
       <c r="D6" t="n">
-        <v>49.16765648040073</v>
+        <v>7.989744178065119</v>
       </c>
       <c r="E6" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F6" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.10119641766548</v>
+        <v>3.591444417870641</v>
       </c>
       <c r="D7" t="n">
-        <v>19.09188309203678</v>
+        <v>3.102431002455978</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F7" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.29634940478971</v>
+        <v>3.460656778278328</v>
       </c>
       <c r="D8" t="n">
-        <v>32.35454888325968</v>
+        <v>5.257614193529698</v>
       </c>
       <c r="E8" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F8" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.72066206726089</v>
+        <v>6.942107585929895</v>
       </c>
       <c r="D9" t="n">
-        <v>24.7339666397442</v>
+        <v>4.019269578958433</v>
       </c>
       <c r="E9" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F9" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.09015799023958</v>
+        <v>6.352150673413933</v>
       </c>
       <c r="D10" t="n">
-        <v>25.06114521951269</v>
+        <v>4.072436098170812</v>
       </c>
       <c r="E10" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F10" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4.854835375799555</v>
+        <v>0.7889107485674276</v>
       </c>
       <c r="D11" t="n">
-        <v>9.934021175934527</v>
+        <v>1.614278441089361</v>
       </c>
       <c r="E11" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F11" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.89134174515891</v>
+        <v>2.419843033588323</v>
       </c>
       <c r="D12" t="n">
-        <v>28.61680776350656</v>
+        <v>4.650231261569815</v>
       </c>
       <c r="E12" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F12" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.60642852763317</v>
+        <v>7.24854463574039</v>
       </c>
       <c r="D13" t="n">
-        <v>8.587157233615988</v>
+        <v>1.395413050462598</v>
       </c>
       <c r="E13" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F13" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.53402957710028</v>
+        <v>5.124279806278796</v>
       </c>
       <c r="D14" t="n">
-        <v>21.40278289566717</v>
+        <v>3.477952220545915</v>
       </c>
       <c r="E14" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F14" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.7643623624816</v>
+        <v>4.99920888390326</v>
       </c>
       <c r="D15" t="n">
-        <v>18.70684466066794</v>
+        <v>3.03986225735854</v>
       </c>
       <c r="E15" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F15" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>51.0733072821418</v>
+        <v>8.299412433348044</v>
       </c>
       <c r="D16" t="n">
-        <v>37.25117590999193</v>
+        <v>6.053316085373688</v>
       </c>
       <c r="E16" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F16" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.60985753610429</v>
+        <v>6.111601849616948</v>
       </c>
       <c r="D17" t="n">
-        <v>24.75535339978303</v>
+        <v>4.022744927464742</v>
       </c>
       <c r="E17" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F17" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.91443130199808</v>
+        <v>6.973595086574688</v>
       </c>
       <c r="D18" t="n">
-        <v>35.10857548064136</v>
+        <v>5.705143515604222</v>
       </c>
       <c r="E18" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F18" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>52.20478582179825</v>
+        <v>8.483277696042215</v>
       </c>
       <c r="D19" t="n">
-        <v>31.16409537690846</v>
+        <v>5.064165498747625</v>
       </c>
       <c r="E19" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F19" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>8.34697060300423</v>
+        <v>1.356382722988188</v>
       </c>
       <c r="D20" t="n">
-        <v>8.593800727626581</v>
+        <v>1.39649261823932</v>
       </c>
       <c r="E20" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F20" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>6.019287700136061</v>
+        <v>0.9781342512721098</v>
       </c>
       <c r="D21" t="n">
-        <v>6.837615402269123</v>
+        <v>1.111112502868733</v>
       </c>
       <c r="E21" t="n">
-        <v>17.16088806237524</v>
+        <v>2.788644310135977</v>
       </c>
       <c r="F21" t="n">
-        <v>13.86338785340135</v>
+        <v>2.25280052617772</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
